--- a/Export-ArFilter.xlsx
+++ b/Export-ArFilter.xlsx
@@ -15,7 +15,7 @@
     <sheet name="الجدول" sheetId="3" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">الجدول!$A$1:$AC$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">الجدول!$A$1:$T$1</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>العدد</t>
   </si>
@@ -73,25 +73,6 @@
     <t>العنـــــــــــــــــــــــــــــــــــــــــوان</t>
   </si>
   <si>
-    <t>لقـــب الــزوج(ة)</t>
-  </si>
-  <si>
-    <t>تاريـخ ميـــلاد
- الـــــــــزوج (ة)</t>
-  </si>
-  <si>
-    <t>رقم عقد ميلاد الـــزوج(ة)</t>
-  </si>
-  <si>
-    <t>بلـــدية ميــــــلاد الـــــــــــــزوج(ة)</t>
-  </si>
-  <si>
-    <t>اســم أم الـــــزوج (ة)</t>
-  </si>
-  <si>
-    <t>لقـــب أم الــزوج(ة)</t>
-  </si>
-  <si>
     <t>مستوى
 المداخيل</t>
   </si>
@@ -112,108 +93,6 @@
   </si>
   <si>
     <t>الملاحظـــــــــــــــــــــــــــة</t>
-  </si>
-  <si>
-    <r>
-      <t>اســــم 
-الـــزوج(</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="20"/>
-        <color indexed="10"/>
-        <rFont val="Mohammad Bold Normal"/>
-        <charset val="178"/>
-      </rPr>
-      <t>ة</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="20"/>
-        <color indexed="8"/>
-        <rFont val="Mohammad Bold Normal"/>
-        <charset val="178"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>اســـــــم أب الـــــزوج(</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="20"/>
-        <color indexed="10"/>
-        <rFont val="Mohammad Bold Normal"/>
-        <charset val="178"/>
-      </rPr>
-      <t>ة</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="20"/>
-        <color indexed="8"/>
-        <rFont val="Mohammad Bold Normal"/>
-        <charset val="178"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">الفئـة
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="20"/>
-        <color indexed="10"/>
-        <rFont val="Mohammad Head"/>
-      </rPr>
-      <t xml:space="preserve"> ( </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="20"/>
-        <color indexed="8"/>
-        <rFont val="Mohammad Head"/>
-      </rPr>
-      <t>أكـبـر</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="20"/>
-        <color indexed="10"/>
-        <rFont val="Mohammad Head"/>
-      </rPr>
-      <t xml:space="preserve">/ </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="20"/>
-        <color indexed="8"/>
-        <rFont val="Mohammad Head"/>
-      </rPr>
-      <t>أقــل</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="20"/>
-        <color indexed="10"/>
-        <rFont val="Mohammad Head"/>
-      </rPr>
-      <t>)</t>
-    </r>
   </si>
 </sst>
 </file>
@@ -223,7 +102,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_-* #,##0.00\ &quot;€&quot;_-;\-* #,##0.00\ &quot;€&quot;_-;_-* &quot;-&quot;??\ &quot;€&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="18">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -289,20 +168,6 @@
     <font>
       <b/>
       <sz val="20"/>
-      <color indexed="10"/>
-      <name val="Mohammad Bold Normal"/>
-      <charset val="178"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="20"/>
-      <color indexed="8"/>
-      <name val="Mohammad Bold Normal"/>
-      <charset val="178"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="20"/>
       <color rgb="FFCC00CC"/>
       <name val="Mohammad Bold Normal"/>
       <charset val="178"/>
@@ -313,24 +178,6 @@
       <color rgb="FF0000CC"/>
       <name val="Mohammad Bold Normal"/>
       <charset val="178"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="20"/>
-      <color theme="1"/>
-      <name val="Mohammad Head"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="20"/>
-      <color indexed="10"/>
-      <name val="Mohammad Head"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="20"/>
-      <color indexed="8"/>
-      <name val="Mohammad Head"/>
     </font>
     <font>
       <b/>
@@ -478,13 +325,13 @@
       <alignment horizontal="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
@@ -512,16 +359,13 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
   </cellXfs>
@@ -539,7 +383,7 @@
     <cellStyle name="Style 2 2" xfId="11"/>
     <cellStyle name="Style 6" xfId="4"/>
   </cellStyles>
-  <dxfs count="31">
+  <dxfs count="22">
     <dxf>
       <font>
         <b/>
@@ -563,303 +407,6 @@
           <color indexed="64"/>
         </left>
         <right/>
-        <top style="double">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="20"/>
-        <color theme="1"/>
-        <name val="Mohammad Bold Normal"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="2"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="double">
-          <color indexed="64"/>
-        </left>
-        <right style="double">
-          <color indexed="64"/>
-        </right>
-        <top style="double">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="20"/>
-        <color theme="1"/>
-        <name val="Mohammad Bold Normal"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="2"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="double">
-          <color indexed="64"/>
-        </left>
-        <right style="double">
-          <color indexed="64"/>
-        </right>
-        <top style="double">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="20"/>
-        <color theme="1"/>
-        <name val="Mohammad Bold Normal"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="2"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="double">
-          <color indexed="64"/>
-        </left>
-        <right style="double">
-          <color indexed="64"/>
-        </right>
-        <top style="double">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="20"/>
-        <color theme="1"/>
-        <name val="Mohammad Bold Normal"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="2"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="double">
-          <color indexed="64"/>
-        </left>
-        <right style="double">
-          <color indexed="64"/>
-        </right>
-        <top style="double">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="20"/>
-        <color theme="1"/>
-        <name val="Mohammad Bold Normal"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="2"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="double">
-          <color indexed="64"/>
-        </left>
-        <right style="double">
-          <color indexed="64"/>
-        </right>
-        <top style="double">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="20"/>
-        <color theme="1"/>
-        <name val="Mohammad Bold Normal"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="2"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="double">
-          <color indexed="64"/>
-        </left>
-        <right style="double">
-          <color indexed="64"/>
-        </right>
-        <top style="double">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="20"/>
-        <color theme="1"/>
-        <name val="Mohammad Bold Normal"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="2"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="double">
-          <color indexed="64"/>
-        </left>
-        <right style="double">
-          <color indexed="64"/>
-        </right>
-        <top style="double">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="20"/>
-        <color theme="1"/>
-        <name val="Mohammad Bold Normal"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="2"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="double">
-          <color indexed="64"/>
-        </left>
-        <right style="double">
-          <color indexed="64"/>
-        </right>
-        <top style="double">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="20"/>
-        <color theme="1"/>
-        <name val="Mohammad Bold Normal"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="2"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="double">
-          <color indexed="64"/>
-        </left>
-        <right style="double">
-          <color indexed="64"/>
-        </right>
         <top style="double">
           <color indexed="64"/>
         </top>
@@ -1540,32 +1087,23 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:AC2" totalsRowShown="0" dataDxfId="30" tableBorderDxfId="29">
-  <autoFilter ref="A1:AC2"/>
-  <tableColumns count="29">
-    <tableColumn id="1" name="العدد" dataDxfId="28"/>
-    <tableColumn id="2" name="رقـــم _x000a_الملــــــف" dataDxfId="27"/>
-    <tableColumn id="3" name="تاريــــخ _x000a_الايـــداع" dataDxfId="26"/>
-    <tableColumn id="4" name="اللقــــب" dataDxfId="25"/>
-    <tableColumn id="5" name="الاســــم" dataDxfId="24"/>
-    <tableColumn id="6" name="الجنس" dataDxfId="23"/>
-    <tableColumn id="7" name="تاريخ الميلاد" dataDxfId="22"/>
-    <tableColumn id="8" name="رقـم عقد الميـــــلاد" dataDxfId="21"/>
-    <tableColumn id="9" name="بلــدية الميــــلاد" dataDxfId="20"/>
-    <tableColumn id="10" name="الحالة العائلية" dataDxfId="19"/>
-    <tableColumn id="11" name="اســــــــم الاب" dataDxfId="18"/>
-    <tableColumn id="12" name="لقــــــب الام" dataDxfId="17"/>
-    <tableColumn id="13" name="اســــم الام" dataDxfId="16"/>
-    <tableColumn id="14" name="العنـــــــــــــــــــــــــــــــــــــــــوان" dataDxfId="15"/>
-    <tableColumn id="15" name="اســــم _x000a_الـــزوج(ة)" dataDxfId="14"/>
-    <tableColumn id="16" name="لقـــب الــزوج(ة)" dataDxfId="13"/>
-    <tableColumn id="17" name="تاريـخ ميـــلاد_x000a_ الـــــــــزوج (ة)" dataDxfId="12"/>
-    <tableColumn id="18" name="رقم عقد ميلاد الـــزوج(ة)" dataDxfId="11"/>
-    <tableColumn id="19" name="بلـــدية ميــــــلاد الـــــــــــــزوج(ة)" dataDxfId="10"/>
-    <tableColumn id="20" name="اســـــــم أب الـــــزوج(ة)" dataDxfId="9"/>
-    <tableColumn id="21" name="اســم أم الـــــزوج (ة)" dataDxfId="8"/>
-    <tableColumn id="22" name="لقـــب أم الــزوج(ة)" dataDxfId="7"/>
-    <tableColumn id="23" name="الفئـة_x000a_ ( أكـبـر/ أقــل)" dataDxfId="6"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Table4" displayName="Table4" ref="A1:T2" totalsRowShown="0" dataDxfId="21" tableBorderDxfId="20">
+  <autoFilter ref="A1:T2"/>
+  <tableColumns count="20">
+    <tableColumn id="1" name="العدد" dataDxfId="19"/>
+    <tableColumn id="2" name="رقـــم _x000a_الملــــــف" dataDxfId="18"/>
+    <tableColumn id="3" name="تاريــــخ _x000a_الايـــداع" dataDxfId="17"/>
+    <tableColumn id="4" name="اللقــــب" dataDxfId="16"/>
+    <tableColumn id="5" name="الاســــم" dataDxfId="15"/>
+    <tableColumn id="6" name="الجنس" dataDxfId="14"/>
+    <tableColumn id="7" name="تاريخ الميلاد" dataDxfId="13"/>
+    <tableColumn id="8" name="رقـم عقد الميـــــلاد" dataDxfId="12"/>
+    <tableColumn id="9" name="بلــدية الميــــلاد" dataDxfId="11"/>
+    <tableColumn id="10" name="الحالة العائلية" dataDxfId="10"/>
+    <tableColumn id="11" name="اســــــــم الاب" dataDxfId="9"/>
+    <tableColumn id="12" name="لقــــــب الام" dataDxfId="8"/>
+    <tableColumn id="13" name="اســــم الام" dataDxfId="7"/>
+    <tableColumn id="14" name="العنـــــــــــــــــــــــــــــــــــــــــوان" dataDxfId="6"/>
     <tableColumn id="24" name="مستوى_x000a_المداخيل" dataDxfId="5"/>
     <tableColumn id="25" name="ظروف_x000a_السكن" dataDxfId="4"/>
     <tableColumn id="26" name="الحالة_x000a_العائلية" dataDxfId="3"/>
@@ -1841,7 +1379,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AC2"/>
+  <dimension ref="A1:T2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.42578125" bestFit="1" customWidth="1"/>
@@ -1857,24 +1395,15 @@
     <col min="12" max="12" width="18.140625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="15.85546875" customWidth="1"/>
     <col min="14" max="14" width="51.85546875" customWidth="1"/>
-    <col min="15" max="15" width="24.85546875" customWidth="1"/>
-    <col min="16" max="16" width="23.85546875" customWidth="1"/>
-    <col min="17" max="17" width="26" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="35" customWidth="1"/>
-    <col min="19" max="19" width="44.140625" customWidth="1"/>
-    <col min="20" max="20" width="34.7109375" customWidth="1"/>
-    <col min="21" max="21" width="29.7109375" customWidth="1"/>
-    <col min="22" max="22" width="27.28515625" customWidth="1"/>
-    <col min="23" max="23" width="31.42578125" customWidth="1"/>
-    <col min="24" max="24" width="17" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="16" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="22.42578125" customWidth="1"/>
-    <col min="27" max="27" width="34.7109375" customWidth="1"/>
-    <col min="28" max="28" width="23.140625" customWidth="1"/>
-    <col min="29" max="29" width="47.5703125" customWidth="1"/>
+    <col min="15" max="15" width="17" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="16" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="22.42578125" customWidth="1"/>
+    <col min="18" max="18" width="34.7109375" customWidth="1"/>
+    <col min="19" max="19" width="23.140625" customWidth="1"/>
+    <col min="20" max="20" width="47.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" s="1" customFormat="1" ht="53.25" thickBot="1">
+    <row r="1" spans="1:20" s="1" customFormat="1" ht="53.25" thickBot="1">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -1917,53 +1446,26 @@
       <c r="N1" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="P1" s="9" t="s">
+      <c r="O1" s="12" t="s">
         <v>14</v>
       </c>
+      <c r="P1" s="14" t="s">
+        <v>15</v>
+      </c>
       <c r="Q1" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="R1" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="S1" s="12" t="s">
+      <c r="R1" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="T1" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="9" t="s">
+      <c r="S1" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="V1" s="10" t="s">
+      <c r="T1" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="W1" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="X1" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="Y1" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="Z1" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="AA1" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="AB1" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="AC1" s="16" t="s">
-        <v>25</v>
-      </c>
     </row>
-    <row r="2" spans="1:29" s="3" customFormat="1" ht="27" thickTop="1">
+    <row r="2" spans="1:20" s="3" customFormat="1" ht="27" thickTop="1">
       <c r="A2" s="4"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -1983,16 +1485,7 @@
       <c r="Q2" s="2"/>
       <c r="R2" s="2"/>
       <c r="S2" s="2"/>
-      <c r="T2" s="2"/>
-      <c r="U2" s="2"/>
-      <c r="V2" s="2"/>
-      <c r="W2" s="2"/>
-      <c r="X2" s="2"/>
-      <c r="Y2" s="2"/>
-      <c r="Z2" s="2"/>
-      <c r="AA2" s="2"/>
-      <c r="AB2" s="2"/>
-      <c r="AC2" s="5"/>
+      <c r="T2" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
